--- a/results/fire_and_explosion_index.xlsx
+++ b/results/fire_and_explosion_index.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25FDAA1-6E5D-4075-81E2-9ABC043E4672}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDE8AA7-B112-4459-942F-7AF73285DDD7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="16725" activeTab="1" xr2:uid="{27E07CFF-33E2-45AC-A1B7-5E8839713283}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="16725" activeTab="2" xr2:uid="{27E07CFF-33E2-45AC-A1B7-5E8839713283}"/>
   </bookViews>
   <sheets>
     <sheet name="5-step" sheetId="1" r:id="rId1"/>
     <sheet name="1-step" sheetId="2" r:id="rId2"/>
+    <sheet name="AO" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="42">
   <si>
     <t>Base factor</t>
   </si>
@@ -159,6 +160,24 @@
   </si>
   <si>
     <t>Base Maximum Probable Property Damage (MM$)</t>
+  </si>
+  <si>
+    <t>kcal/mol</t>
+  </si>
+  <si>
+    <t>g/mol</t>
+  </si>
+  <si>
+    <t>kcal/g</t>
+  </si>
+  <si>
+    <t>Btu/g</t>
+  </si>
+  <si>
+    <t>Btu/kg</t>
+  </si>
+  <si>
+    <t>Btu/lb</t>
   </si>
 </sst>
 </file>
@@ -226,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -251,6 +270,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,10 +595,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -598,10 +620,10 @@
       <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" s="16"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -673,10 +695,10 @@
       <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="5"/>
+      <c r="B15" s="16"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -919,10 +941,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -944,10 +966,10 @@
       <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" s="16"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -1019,10 +1041,10 @@
       <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="5"/>
+      <c r="B15" s="16"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -1242,6 +1264,399 @@
       <c r="B43" s="9">
         <f>B42/30*17162504.3610041*0.7/10^6</f>
         <v>11.233569786090367</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A15:B15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FF490C7-F5B6-4F3C-9A3D-901209F0C3B6}">
+  <dimension ref="A1:O43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="16"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="10">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="16"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="N7" s="1">
+        <v>100</v>
+      </c>
+      <c r="O7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>2.016</v>
+      </c>
+      <c r="O8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <f>N7/N8</f>
+        <v>49.603174603174601</v>
+      </c>
+      <c r="O9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="7">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <f>N9*3.96567</f>
+        <v>196.70982142857142</v>
+      </c>
+      <c r="O10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="7">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <f>N10*1000</f>
+        <v>196709.82142857142</v>
+      </c>
+      <c r="O11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="7">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <f>N11/2.20462</f>
+        <v>89226.180216350869</v>
+      </c>
+      <c r="O12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="9">
+        <f>SUM(B6:B12)</f>
+        <v>1.5</v>
+      </c>
+      <c r="N13">
+        <f>N12*6</f>
+        <v>535357.08129810519</v>
+      </c>
+      <c r="O13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="16"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="7">
+        <f>10^(0.17179+0.42988*LOG(2469.37499350752*N13*2.20462/10^9)-0.37244*LOG(2469.37499350752*N13*2.20462/10^9)^2+0.17712*LOG(2469.37499350752*N13*2.20462/10^9)^3-0.029984*LOG(2469.37499350752*N13*2.20462/10^9)^4)</f>
+        <v>2.0299192462244537</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="9">
+        <f>SUM(B16:B28)</f>
+        <v>3.5299192462244537</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="9">
+        <f>B13*B29</f>
+        <v>5.2948788693366806</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="12">
+        <f>B31*B3</f>
+        <v>111.19245625607029</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="9">
+        <f>B33*0.84*0.3048</f>
+        <v>28.468826960154189</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="9">
+        <f>PI()*B34^2</f>
+        <v>2546.1795051481308</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="15">
+        <v>10.943213148596207</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="15">
+        <f>B36*0.82</f>
+        <v>8.9734347818488889</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="15">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="15">
+        <f>B37*B38</f>
+        <v>1.7946869563697778</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" s="15">
+        <f>B39*B40</f>
+        <v>1.7946869563697778</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="9">
+        <f>10^(1.325132+0.592471*LOG(B41))</f>
+        <v>29.895990227273522</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="9">
+        <f>B42/30*17162504.3610041*0.7/10^6</f>
+        <v>11.972101461882747</v>
       </c>
     </row>
   </sheetData>

--- a/results/fire_and_explosion_index.xlsx
+++ b/results/fire_and_explosion_index.xlsx
@@ -8,14 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDE8AA7-B112-4459-942F-7AF73285DDD7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C605F4-117B-4A90-854C-034A8C825A24}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="16725" activeTab="2" xr2:uid="{27E07CFF-33E2-45AC-A1B7-5E8839713283}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="12105" activeTab="7" xr2:uid="{27E07CFF-33E2-45AC-A1B7-5E8839713283}"/>
   </bookViews>
   <sheets>
     <sheet name="5-step" sheetId="1" r:id="rId1"/>
     <sheet name="1-step" sheetId="2" r:id="rId2"/>
     <sheet name="AO" sheetId="3" r:id="rId3"/>
+    <sheet name="storage_N2O" sheetId="5" r:id="rId4"/>
+    <sheet name="transport_N2O" sheetId="9" r:id="rId5"/>
+    <sheet name="benzene_N2O" sheetId="11" r:id="rId6"/>
+    <sheet name="benzene_H2O2" sheetId="12" r:id="rId7"/>
+    <sheet name="cumene" sheetId="13" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="71">
   <si>
     <t>Base factor</t>
   </si>
@@ -179,11 +184,101 @@
   <si>
     <t>Btu/lb</t>
   </si>
+  <si>
+    <t>Credit factors</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>Emergency power</t>
+  </si>
+  <si>
+    <t>Cooling</t>
+  </si>
+  <si>
+    <t>Explosion control</t>
+  </si>
+  <si>
+    <t>Emergency shutdown</t>
+  </si>
+  <si>
+    <t>Computer control</t>
+  </si>
+  <si>
+    <t>Inert gas</t>
+  </si>
+  <si>
+    <t>Operating instructions</t>
+  </si>
+  <si>
+    <t>Reactive chemical review</t>
+  </si>
+  <si>
+    <t>Other process harzard analysis</t>
+  </si>
+  <si>
+    <t>Loss control credit factor (max)</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>Remote control valves</t>
+  </si>
+  <si>
+    <t>Dump/blowdown</t>
+  </si>
+  <si>
+    <t>Drainage</t>
+  </si>
+  <si>
+    <t>Interlock</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Leak detection</t>
+  </si>
+  <si>
+    <t>Structural steel</t>
+  </si>
+  <si>
+    <t>Fire water supply</t>
+  </si>
+  <si>
+    <t>Special systems</t>
+  </si>
+  <si>
+    <t>Sprinkler systems</t>
+  </si>
+  <si>
+    <t>Water curtains</t>
+  </si>
+  <si>
+    <t>Foam</t>
+  </si>
+  <si>
+    <t>Hand extinguishes/monitors</t>
+  </si>
+  <si>
+    <t>Cable protection</t>
+  </si>
+  <si>
+    <t>Nf = 0</t>
+  </si>
+  <si>
+    <t>Nr = 1</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -245,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -273,6 +368,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,18 +698,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBD5DBF6-C07A-4F80-85FA-3366F951286F}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -620,10 +735,10 @@
       <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="16"/>
+      <c r="B5" s="20"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -695,10 +810,10 @@
       <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="16"/>
+      <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -708,7 +823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>10</v>
       </c>
@@ -717,7 +832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>11</v>
       </c>
@@ -725,7 +840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>12</v>
       </c>
@@ -733,7 +848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>13</v>
       </c>
@@ -741,7 +856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>14</v>
       </c>
@@ -749,7 +864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
@@ -757,7 +872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>16</v>
       </c>
@@ -766,7 +881,7 @@
         <v>1.9214739304102686</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>17</v>
       </c>
@@ -774,7 +889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>18</v>
       </c>
@@ -782,7 +897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>19</v>
       </c>
@@ -790,7 +905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>20</v>
       </c>
@@ -798,7 +913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>21</v>
       </c>
@@ -806,7 +921,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>8</v>
       </c>
@@ -815,7 +930,7 @@
         <v>3.4214739304102686</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>24</v>
       </c>
@@ -824,7 +939,12 @@
         <v>8.2115374329846436</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>7</v>
       </c>
@@ -832,8 +952,29 @@
         <f>B31*B3</f>
         <v>238.13458555655467</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="1">
+        <f>G34*G35*G36*G37*G38*G39*G40*G41*G42</f>
+        <v>0.85058224727715992</v>
+      </c>
+      <c r="I33" t="s">
+        <v>54</v>
+      </c>
+      <c r="J33" s="1">
+        <f>J34*J35*J36*J37</f>
+        <v>0.91295623999999986</v>
+      </c>
+      <c r="L33" t="s">
+        <v>59</v>
+      </c>
+      <c r="M33" s="1">
+        <f>M34*M35*M36*M37*M38*M39*M40*M41*M42</f>
+        <v>0.75073553589384012</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>29</v>
       </c>
@@ -841,8 +982,26 @@
         <f>B33*0.84*0.3048</f>
         <v>60.970074209215809</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34">
+        <v>0.98</v>
+      </c>
+      <c r="I34" t="s">
+        <v>55</v>
+      </c>
+      <c r="J34">
+        <v>0.98</v>
+      </c>
+      <c r="L34" t="s">
+        <v>60</v>
+      </c>
+      <c r="M34">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>30</v>
       </c>
@@ -850,16 +1009,52 @@
         <f>PI()*B34^2</f>
         <v>11678.399290843583</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F35" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35">
+        <v>0.99</v>
+      </c>
+      <c r="I35" t="s">
+        <v>56</v>
+      </c>
+      <c r="J35">
+        <v>0.98</v>
+      </c>
+      <c r="L35" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B36" s="15">
         <v>41.714185454513995</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F36" t="s">
+        <v>46</v>
+      </c>
+      <c r="G36">
+        <v>0.98</v>
+      </c>
+      <c r="I36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J36">
+        <v>0.97</v>
+      </c>
+      <c r="L36" t="s">
+        <v>62</v>
+      </c>
+      <c r="M36">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>32</v>
       </c>
@@ -867,16 +1062,46 @@
         <f>B36*0.82</f>
         <v>34.205632072701476</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F37" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37">
+        <v>0.99</v>
+      </c>
+      <c r="I37" t="s">
+        <v>58</v>
+      </c>
+      <c r="J37">
+        <v>0.98</v>
+      </c>
+      <c r="L37" t="s">
+        <v>63</v>
+      </c>
+      <c r="M37">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>33</v>
       </c>
       <c r="B38" s="15">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F38" t="s">
+        <v>48</v>
+      </c>
+      <c r="G38">
+        <v>0.99</v>
+      </c>
+      <c r="L38" t="s">
+        <v>64</v>
+      </c>
+      <c r="M38">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>35</v>
       </c>
@@ -884,16 +1109,40 @@
         <f>B37*B38</f>
         <v>32.495350469066402</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F39" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39">
+        <v>0.96</v>
+      </c>
+      <c r="L39" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B40" s="15">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F40" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40">
+        <v>0.99</v>
+      </c>
+      <c r="L40" t="s">
+        <v>66</v>
+      </c>
+      <c r="M40">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>27</v>
       </c>
@@ -901,8 +1150,20 @@
         <f>B39*B40</f>
         <v>32.495350469066402</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F41" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41">
+        <v>0.98</v>
+      </c>
+      <c r="L41" t="s">
+        <v>67</v>
+      </c>
+      <c r="M41">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>28</v>
       </c>
@@ -910,14 +1171,62 @@
         <f>10^(1.325132+0.592471*LOG(B41))</f>
         <v>166.28084896025334</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F42" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42">
+        <v>0.98</v>
+      </c>
+      <c r="L42" t="s">
+        <v>68</v>
+      </c>
+      <c r="M42">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>34</v>
       </c>
       <c r="B43" s="9">
         <f>B42/30*22841424.5645393*0.7/10^6</f>
         <v>88.622134254574178</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="22">
+        <f>G33*J33*M33</f>
+        <v>0.58297945397118356</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" s="22">
+        <f>B39*B46</f>
+        <v>18.944121673058575</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" s="23">
+        <f>10^(1.325132+0.592471*LOG(B47))</f>
+        <v>120.7809884090839</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="23">
+        <f>B48/30*22841424.5645393*0.7/10^6</f>
+        <v>64.372229496786986</v>
       </c>
     </row>
   </sheetData>
@@ -933,18 +1242,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F83637B7-417A-41EB-BD1C-082C8FD22B0D}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -966,10 +1281,10 @@
       <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="16"/>
+      <c r="B5" s="20"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -1041,10 +1356,10 @@
       <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="16"/>
+      <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -1054,7 +1369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>10</v>
       </c>
@@ -1063,7 +1378,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>11</v>
       </c>
@@ -1071,7 +1386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>12</v>
       </c>
@@ -1079,7 +1394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>13</v>
       </c>
@@ -1087,7 +1402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>14</v>
       </c>
@@ -1095,7 +1410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
@@ -1103,7 +1418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>16</v>
       </c>
@@ -1112,7 +1427,7 @@
         <v>1.0646907348259158</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>17</v>
       </c>
@@ -1120,7 +1435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>18</v>
       </c>
@@ -1128,7 +1443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>19</v>
       </c>
@@ -1136,7 +1451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>20</v>
       </c>
@@ -1144,7 +1459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>21</v>
       </c>
@@ -1152,7 +1467,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>8</v>
       </c>
@@ -1161,7 +1476,7 @@
         <v>3.1646907348259159</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>24</v>
       </c>
@@ -1170,16 +1485,42 @@
         <v>4.7470361022388738</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="19">
         <f>B31*B3</f>
         <v>47.470361022388737</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="1">
+        <f>G34*G35*G36*G37*G38*G39*G40*G41*G42</f>
+        <v>0.85058224727715992</v>
+      </c>
+      <c r="I33" t="s">
+        <v>54</v>
+      </c>
+      <c r="J33" s="1">
+        <f>J34*J35*J36*J37</f>
+        <v>0.91295623999999986</v>
+      </c>
+      <c r="L33" t="s">
+        <v>59</v>
+      </c>
+      <c r="M33" s="1">
+        <f>M34*M35*M36*M37*M38*M39*M40*M41*M42</f>
+        <v>0.75073553589384012</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>29</v>
       </c>
@@ -1187,8 +1528,26 @@
         <f>B33*0.84*0.3048</f>
         <v>12.153931473284233</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34">
+        <v>0.98</v>
+      </c>
+      <c r="I34" t="s">
+        <v>55</v>
+      </c>
+      <c r="J34">
+        <v>0.98</v>
+      </c>
+      <c r="L34" t="s">
+        <v>60</v>
+      </c>
+      <c r="M34">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>30</v>
       </c>
@@ -1196,16 +1555,52 @@
         <f>PI()*B34^2</f>
         <v>464.06994149090718</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F35" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35">
+        <v>0.99</v>
+      </c>
+      <c r="I35" t="s">
+        <v>56</v>
+      </c>
+      <c r="J35">
+        <v>0.98</v>
+      </c>
+      <c r="L35" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B36" s="15">
         <v>9.8281441373388834</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F36" t="s">
+        <v>46</v>
+      </c>
+      <c r="G36">
+        <v>0.98</v>
+      </c>
+      <c r="I36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J36">
+        <v>0.97</v>
+      </c>
+      <c r="L36" t="s">
+        <v>62</v>
+      </c>
+      <c r="M36">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>32</v>
       </c>
@@ -1213,16 +1608,46 @@
         <f>B36*0.82</f>
         <v>8.0590781926178838</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F37" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37">
+        <v>0.99</v>
+      </c>
+      <c r="I37" t="s">
+        <v>58</v>
+      </c>
+      <c r="J37">
+        <v>0.98</v>
+      </c>
+      <c r="L37" t="s">
+        <v>63</v>
+      </c>
+      <c r="M37">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>33</v>
       </c>
       <c r="B38" s="15">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F38" t="s">
+        <v>48</v>
+      </c>
+      <c r="G38">
+        <v>0.99</v>
+      </c>
+      <c r="L38" t="s">
+        <v>64</v>
+      </c>
+      <c r="M38">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>35</v>
       </c>
@@ -1230,25 +1655,61 @@
         <f>B37*B38</f>
         <v>1.6118156385235769</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F39" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39">
+        <v>0.96</v>
+      </c>
+      <c r="L39" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>26</v>
       </c>
       <c r="B40" s="15">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F40" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40">
+        <v>0.99</v>
+      </c>
+      <c r="L40" t="s">
+        <v>66</v>
+      </c>
+      <c r="M40">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="18">
         <f>B39*B40</f>
         <v>1.6118156385235769</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F41" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41">
+        <v>0.98</v>
+      </c>
+      <c r="L41" t="s">
+        <v>67</v>
+      </c>
+      <c r="M41">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>28</v>
       </c>
@@ -1256,14 +1717,62 @@
         <f>10^(1.325132+0.592471*LOG(B41))</f>
         <v>28.051774670604765</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F42" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42">
+        <v>0.98</v>
+      </c>
+      <c r="L42" t="s">
+        <v>68</v>
+      </c>
+      <c r="M42">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>34</v>
       </c>
       <c r="B43" s="9">
         <f>B42/30*17162504.3610041*0.7/10^6</f>
         <v>11.233569786090367</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="22">
+        <f>G33*J33*M33</f>
+        <v>0.58297945397118356</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" s="22">
+        <f>B39*B46</f>
+        <v>0.93965540084868948</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" s="23">
+        <f>10^(1.325132+0.592471*LOG(B47))</f>
+        <v>20.375894713855029</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="23">
+        <f>B48/30*22841424.5645393*0.7/10^6</f>
+        <v>10.859670780968676</v>
       </c>
     </row>
   </sheetData>
@@ -1279,19 +1788,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FF490C7-F5B6-4F3C-9A3D-901209F0C3B6}">
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -1313,10 +1829,10 @@
       <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="16"/>
+      <c r="B5" s="20"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -1435,16 +1951,558 @@
       <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="16"/>
+      <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B16" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="7">
+        <f>10^(0.17179+0.42988*LOG(2469.37499350752*N13*2.20462/10^9)-0.37244*LOG(2469.37499350752*N13*2.20462/10^9)^2+0.17712*LOG(2469.37499350752*N13*2.20462/10^9)^3-0.029984*LOG(2469.37499350752*N13*2.20462/10^9)^4)</f>
+        <v>2.0299192462244537</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="9">
+        <f>SUM(B16:B28)</f>
+        <v>3.5299192462244537</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="9">
+        <f>B13*B29</f>
+        <v>5.2948788693366806</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="19">
+        <f>B31*B3</f>
+        <v>111.19245625607029</v>
+      </c>
+      <c r="F33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="1">
+        <f>G34*G35*G36*G37*G38*G39*G40*G41*G42</f>
+        <v>0.85058224727715992</v>
+      </c>
+      <c r="I33" t="s">
+        <v>54</v>
+      </c>
+      <c r="J33" s="1">
+        <f>J34*J35*J36*J37</f>
+        <v>0.91295623999999986</v>
+      </c>
+      <c r="L33" t="s">
+        <v>59</v>
+      </c>
+      <c r="M33" s="1">
+        <f>M34*M35*M36*M37*M38*M39*M40*M41*M42</f>
+        <v>0.75073553589384012</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="9">
+        <f>B33*0.84*0.3048</f>
+        <v>28.468826960154189</v>
+      </c>
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34">
+        <v>0.98</v>
+      </c>
+      <c r="I34" t="s">
+        <v>55</v>
+      </c>
+      <c r="J34">
+        <v>0.98</v>
+      </c>
+      <c r="L34" t="s">
+        <v>60</v>
+      </c>
+      <c r="M34">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="9">
+        <f>PI()*B34^2</f>
+        <v>2546.1795051481308</v>
+      </c>
+      <c r="F35" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35">
+        <v>0.99</v>
+      </c>
+      <c r="I35" t="s">
+        <v>56</v>
+      </c>
+      <c r="J35">
+        <v>0.98</v>
+      </c>
+      <c r="L35" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="15">
+        <v>10.943213148596207</v>
+      </c>
+      <c r="F36" t="s">
+        <v>46</v>
+      </c>
+      <c r="G36">
+        <v>0.98</v>
+      </c>
+      <c r="I36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J36">
+        <v>0.97</v>
+      </c>
+      <c r="L36" t="s">
+        <v>62</v>
+      </c>
+      <c r="M36">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="15">
+        <f>B36*0.82</f>
+        <v>8.9734347818488889</v>
+      </c>
+      <c r="F37" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37">
+        <v>0.99</v>
+      </c>
+      <c r="I37" t="s">
+        <v>58</v>
+      </c>
+      <c r="J37">
+        <v>0.98</v>
+      </c>
+      <c r="L37" t="s">
+        <v>63</v>
+      </c>
+      <c r="M37">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="F38" t="s">
+        <v>48</v>
+      </c>
+      <c r="G38">
+        <v>0.99</v>
+      </c>
+      <c r="L38" t="s">
+        <v>64</v>
+      </c>
+      <c r="M38">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="15">
+        <f>B37*B38</f>
+        <v>1.7946869563697778</v>
+      </c>
+      <c r="F39" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39">
+        <v>0.96</v>
+      </c>
+      <c r="L39" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="15">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40">
+        <v>0.99</v>
+      </c>
+      <c r="L40" t="s">
+        <v>66</v>
+      </c>
+      <c r="M40">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" s="15">
+        <f>B39*B40</f>
+        <v>1.7946869563697778</v>
+      </c>
+      <c r="F41" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41">
+        <v>0.98</v>
+      </c>
+      <c r="L41" t="s">
+        <v>67</v>
+      </c>
+      <c r="M41">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="9">
+        <f>10^(1.325132+0.592471*LOG(B41))</f>
+        <v>29.895990227273522</v>
+      </c>
+      <c r="F42" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42">
+        <v>0.98</v>
+      </c>
+      <c r="L42" t="s">
+        <v>68</v>
+      </c>
+      <c r="M42">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="9">
+        <f>B42/30*17162504.3610041*0.7/10^6</f>
+        <v>11.972101461882747</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="22">
+        <f>G33*J33*M33</f>
+        <v>0.58297945397118356</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" s="22">
+        <f>B39*B46</f>
+        <v>1.0462656218736583</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" s="23">
+        <f>10^(1.325132+0.592471*LOG(B47))</f>
+        <v>21.715472778116098</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="23">
+        <f>B48/30*22841424.5645393*0.7/10^6</f>
+        <v>11.573621111375061</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A15:B15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13DDBBFE-D939-4A99-9993-41CA63A61D3C}">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="20"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="24">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="G4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="20"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="21">
+        <f>SUM(B6:B12)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="20"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="25">
         <v>1</v>
       </c>
     </row>
@@ -1452,15 +2510,15 @@
       <c r="A17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="7">
-        <v>0</v>
+      <c r="B17" s="25">
+        <v>0.2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="25">
         <v>0</v>
       </c>
     </row>
@@ -1468,7 +2526,7 @@
       <c r="A19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="25">
         <v>0</v>
       </c>
     </row>
@@ -1476,7 +2534,7 @@
       <c r="A20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="25">
         <v>0</v>
       </c>
     </row>
@@ -1484,15 +2542,15 @@
       <c r="A21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="7">
-        <v>0</v>
+      <c r="B21" s="25">
+        <v>0.9</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="25">
         <v>0</v>
       </c>
     </row>
@@ -1500,16 +2558,15 @@
       <c r="A23" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="7">
-        <f>10^(0.17179+0.42988*LOG(2469.37499350752*N13*2.20462/10^9)-0.37244*LOG(2469.37499350752*N13*2.20462/10^9)^2+0.17712*LOG(2469.37499350752*N13*2.20462/10^9)^3-0.029984*LOG(2469.37499350752*N13*2.20462/10^9)^4)</f>
-        <v>2.0299192462244537</v>
+      <c r="B23" s="25">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="25">
         <v>0</v>
       </c>
     </row>
@@ -1517,15 +2574,15 @@
       <c r="A25" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="7">
-        <v>0</v>
+      <c r="B25" s="25">
+        <v>0.1</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="25">
         <v>0</v>
       </c>
     </row>
@@ -1533,7 +2590,7 @@
       <c r="A27" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="25">
         <v>0</v>
       </c>
     </row>
@@ -1541,122 +2598,1959 @@
       <c r="A28" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="7">
-        <v>0.5</v>
+      <c r="B28" s="25">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="21">
         <f>SUM(B16:B28)</f>
-        <v>3.5299192462244537</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="21">
         <f>B13*B29</f>
-        <v>5.2948788693366806</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="26">
         <f>B31*B3</f>
-        <v>111.19245625607029</v>
+        <v>30.800000000000004</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="21">
         <f>B33*0.84*0.3048</f>
-        <v>28.468826960154189</v>
+        <v>7.8857856000000011</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="21">
         <f>PI()*B34^2</f>
-        <v>2546.1795051481308</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>195.36186976379892</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A15:B15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3384FA5-C983-4912-8C24-B653BC3C8317}">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="20"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="24">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="G4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="20"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="21">
+        <f>SUM(B6:B12)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="20"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="25">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="25">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="21">
+        <f>SUM(B16:B28)</f>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="21">
+        <f>B13*B29</f>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="26">
+        <f>B31*B3</f>
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="21">
+        <f>B33*0.84*0.3048</f>
+        <v>8.6026752000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="21">
+        <f>PI()*B34^2</f>
+        <v>232.49677062799205</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A15:B15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED6DD1C8-3A48-4DEF-9C76-F9BB6E442DE1}">
+  <dimension ref="A1:M49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="20"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="24">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="20"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="21">
+        <f>SUM(B6:B12)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="20"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="25">
+        <f>0.2*2</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="25">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="25">
+        <f>10^(0.17179+0.42988*LOG(114759*8000*2.20462/10^9)-0.37244*LOG(114759*8000*2.20462/10^9)^2+0.17712*LOG(114759*8000*2.20462/10^9)^3-0.029984*LOG(114759*8000*2.20462/10^9)^4)</f>
+        <v>1.8763929595471995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="21">
+        <f>SUM(B16:B28)</f>
+        <v>4.9763929595471996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="21">
+        <f>B13*B29</f>
+        <v>9.9527859190943992</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="26">
+        <f>B31*B3</f>
+        <v>159.24457470551039</v>
+      </c>
+      <c r="F33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="1">
+        <f>G34*G35*G36*G37*G38*G39*G40*G41*G42</f>
+        <v>0.85058224727715992</v>
+      </c>
+      <c r="I33" t="s">
+        <v>54</v>
+      </c>
+      <c r="J33" s="1">
+        <f>J34*J35*J36*J37</f>
+        <v>0.91295623999999986</v>
+      </c>
+      <c r="L33" t="s">
+        <v>59</v>
+      </c>
+      <c r="M33" s="1">
+        <f>M34*M35*M36*M37*M38*M39*M40*M41*M42</f>
+        <v>0.75073553589384012</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="21">
+        <f>B33*0.84*0.3048</f>
+        <v>40.771706951001242</v>
+      </c>
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34">
+        <v>0.98</v>
+      </c>
+      <c r="I34" t="s">
+        <v>55</v>
+      </c>
+      <c r="J34">
+        <v>0.98</v>
+      </c>
+      <c r="L34" t="s">
+        <v>60</v>
+      </c>
+      <c r="M34">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="21">
+        <f>PI()*B34^2</f>
+        <v>5222.3702745396349</v>
+      </c>
+      <c r="F35" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35">
+        <v>0.99</v>
+      </c>
+      <c r="I35" t="s">
+        <v>56</v>
+      </c>
+      <c r="J35">
+        <v>0.98</v>
+      </c>
+      <c r="L35" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="15">
-        <v>10.943213148596207</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="18">
+        <v>14.18824367492957</v>
+      </c>
+      <c r="F36" t="s">
+        <v>46</v>
+      </c>
+      <c r="G36">
+        <v>0.98</v>
+      </c>
+      <c r="I36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J36">
+        <v>0.97</v>
+      </c>
+      <c r="L36" t="s">
+        <v>62</v>
+      </c>
+      <c r="M36">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>32</v>
       </c>
+      <c r="B37" s="18">
+        <f>B36*0.82</f>
+        <v>11.634359813442247</v>
+      </c>
+      <c r="F37" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37">
+        <v>0.99</v>
+      </c>
+      <c r="I37" t="s">
+        <v>58</v>
+      </c>
+      <c r="J37">
+        <v>0.98</v>
+      </c>
+      <c r="L37" t="s">
+        <v>63</v>
+      </c>
+      <c r="M37">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="18">
+        <v>0.95</v>
+      </c>
+      <c r="F38" t="s">
+        <v>48</v>
+      </c>
+      <c r="G38">
+        <v>0.99</v>
+      </c>
+      <c r="L38" t="s">
+        <v>64</v>
+      </c>
+      <c r="M38">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="18">
+        <f>B37*B38</f>
+        <v>11.052641822770134</v>
+      </c>
+      <c r="F39" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39">
+        <v>0.96</v>
+      </c>
+      <c r="L39" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="18">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40">
+        <v>0.99</v>
+      </c>
+      <c r="L40" t="s">
+        <v>66</v>
+      </c>
+      <c r="M40">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" s="18">
+        <f>B39*B40</f>
+        <v>11.052641822770134</v>
+      </c>
+      <c r="F41" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41">
+        <v>0.98</v>
+      </c>
+      <c r="L41" t="s">
+        <v>67</v>
+      </c>
+      <c r="M41">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="21">
+        <f>10^(1.325132+0.592471*LOG(B41))</f>
+        <v>87.771880173456864</v>
+      </c>
+      <c r="F42" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42">
+        <v>0.98</v>
+      </c>
+      <c r="L42" t="s">
+        <v>68</v>
+      </c>
+      <c r="M42">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="21">
+        <f>B42/30*22841424.5645393*0.7/10^6</f>
+        <v>46.779478196961939</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="15">
+        <f>G33*J33*M33</f>
+        <v>0.58297945397118356</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" s="15">
+        <f>B39*B46</f>
+        <v>6.4434630947775995</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" s="9">
+        <f>10^(1.325132+0.592471*LOG(B47))</f>
+        <v>63.754632648091949</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="9">
+        <f>B48/30*22841424.5645393*0.7/10^6</f>
+        <v>33.979088086330485</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A15:B15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02297EB7-0322-45A8-887E-12D29D5BC0D7}">
+  <dimension ref="A1:M49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="20"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="10">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="20"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="9">
+        <f>SUM(B6:B12)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="20"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="7">
+        <f>0.2*2</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="7">
+        <v>2.1802000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="9">
+        <f>SUM(B16:B28)</f>
+        <v>5.2801999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="21">
+        <f>B13*B29</f>
+        <v>10.5604</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="26">
+        <f>B31*B3</f>
+        <v>168.96639999999999</v>
+      </c>
+      <c r="F33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="1">
+        <f>G34*G35*G36*G37*G38*G39*G40*G41*G42</f>
+        <v>0.85058224727715992</v>
+      </c>
+      <c r="I33" t="s">
+        <v>54</v>
+      </c>
+      <c r="J33" s="1">
+        <f>J34*J35*J36*J37</f>
+        <v>0.91295623999999986</v>
+      </c>
+      <c r="L33" t="s">
+        <v>59</v>
+      </c>
+      <c r="M33" s="1">
+        <f>M34*M35*M36*M37*M38*M39*M40*M41*M42</f>
+        <v>0.75073553589384012</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="21">
+        <f>B33*0.84*0.3048</f>
+        <v>43.260805324799996</v>
+      </c>
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34">
+        <v>0.98</v>
+      </c>
+      <c r="I34" t="s">
+        <v>55</v>
+      </c>
+      <c r="J34">
+        <v>0.98</v>
+      </c>
+      <c r="L34" t="s">
+        <v>60</v>
+      </c>
+      <c r="M34">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="21">
+        <f>PI()*B34^2</f>
+        <v>5879.4820977368245</v>
+      </c>
+      <c r="F35" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35">
+        <v>0.99</v>
+      </c>
+      <c r="I35" t="s">
+        <v>56</v>
+      </c>
+      <c r="J35">
+        <v>0.98</v>
+      </c>
+      <c r="L35" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="15">
+        <v>19.72266322244494</v>
+      </c>
+      <c r="F36" t="s">
+        <v>46</v>
+      </c>
+      <c r="G36">
+        <v>0.98</v>
+      </c>
+      <c r="I36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J36">
+        <v>0.97</v>
+      </c>
+      <c r="L36" t="s">
+        <v>62</v>
+      </c>
+      <c r="M36">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>32</v>
+      </c>
       <c r="B37" s="15">
         <f>B36*0.82</f>
-        <v>8.9734347818488889</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16.172583842404851</v>
+      </c>
+      <c r="F37" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37">
+        <v>0.99</v>
+      </c>
+      <c r="I37" t="s">
+        <v>58</v>
+      </c>
+      <c r="J37">
+        <v>0.98</v>
+      </c>
+      <c r="L37" t="s">
+        <v>63</v>
+      </c>
+      <c r="M37">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>33</v>
       </c>
       <c r="B38" s="15">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+      <c r="F38" t="s">
+        <v>48</v>
+      </c>
+      <c r="G38">
+        <v>0.99</v>
+      </c>
+      <c r="L38" t="s">
+        <v>64</v>
+      </c>
+      <c r="M38">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>35</v>
       </c>
       <c r="B39" s="15">
         <f>B37*B38</f>
-        <v>1.7946869563697778</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15.363954650284608</v>
+      </c>
+      <c r="F39" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39">
+        <v>0.96</v>
+      </c>
+      <c r="L39" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B40" s="15">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F40" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40">
+        <v>0.99</v>
+      </c>
+      <c r="L40" t="s">
+        <v>66</v>
+      </c>
+      <c r="M40">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>27</v>
       </c>
       <c r="B41" s="15">
         <f>B39*B40</f>
-        <v>1.7946869563697778</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>15.363954650284608</v>
+      </c>
+      <c r="F41" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41">
+        <v>0.98</v>
+      </c>
+      <c r="L41" t="s">
+        <v>67</v>
+      </c>
+      <c r="M41">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>28</v>
       </c>
       <c r="B42" s="9">
         <f>10^(1.325132+0.592471*LOG(B41))</f>
-        <v>29.895990227273522</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>106.68432868424418</v>
+      </c>
+      <c r="F42" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42">
+        <v>0.98</v>
+      </c>
+      <c r="L42" t="s">
+        <v>68</v>
+      </c>
+      <c r="M42">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>34</v>
       </c>
       <c r="B43" s="9">
-        <f>B42/30*17162504.3610041*0.7/10^6</f>
-        <v>11.972101461882747</v>
+        <f>B42/30*22841424.5645393*0.7/10^6</f>
+        <v>56.859181070059186</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="15">
+        <f>G33*J33*M33</f>
+        <v>0.58297945397118356</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" s="15">
+        <f>B39*B46</f>
+        <v>8.9568698928609471</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" s="9">
+        <f>10^(1.325132+0.592471*LOG(B47))</f>
+        <v>77.49201875510424</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="9">
+        <f>B48/30*22841424.5645393*0.7/10^6</f>
+        <v>41.300655684133474</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A15:B15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A61A438D-083D-4608-82A6-42C04D2AB3F1}">
+  <dimension ref="A1:M49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="20"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="24">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="20"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="21">
+        <f>SUM(B6:B12)</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="20"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="25">
+        <f>0.2*2</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="25">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="25">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="25">
+        <v>1.9530000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="21">
+        <f>SUM(B16:B28)</f>
+        <v>5.0529999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="21">
+        <f>B13*B29</f>
+        <v>7.5794999999999995</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="26">
+        <f>B31*B3</f>
+        <v>303.17999999999995</v>
+      </c>
+      <c r="F33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="1">
+        <f>G34*G35*G36*G37*G38*G39*G40*G41*G42</f>
+        <v>0.85058224727715992</v>
+      </c>
+      <c r="I33" t="s">
+        <v>54</v>
+      </c>
+      <c r="J33" s="1">
+        <f>J34*J35*J36*J37</f>
+        <v>0.91295623999999986</v>
+      </c>
+      <c r="L33" t="s">
+        <v>59</v>
+      </c>
+      <c r="M33" s="1">
+        <f>M34*M35*M36*M37*M38*M39*M40*M41*M42</f>
+        <v>0.75073553589384012</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="21">
+        <f>B33*0.84*0.3048</f>
+        <v>77.623781759999986</v>
+      </c>
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34">
+        <v>0.98</v>
+      </c>
+      <c r="I34" t="s">
+        <v>55</v>
+      </c>
+      <c r="J34">
+        <v>0.98</v>
+      </c>
+      <c r="L34" t="s">
+        <v>60</v>
+      </c>
+      <c r="M34">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="21">
+        <f>PI()*B34^2</f>
+        <v>18929.514150386891</v>
+      </c>
+      <c r="F35" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35">
+        <v>0.99</v>
+      </c>
+      <c r="I35" t="s">
+        <v>56</v>
+      </c>
+      <c r="J35">
+        <v>0.98</v>
+      </c>
+      <c r="L35" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="15">
+        <v>19.72266322244494</v>
+      </c>
+      <c r="F36" t="s">
+        <v>46</v>
+      </c>
+      <c r="G36">
+        <v>0.98</v>
+      </c>
+      <c r="I36" t="s">
+        <v>57</v>
+      </c>
+      <c r="J36">
+        <v>0.97</v>
+      </c>
+      <c r="L36" t="s">
+        <v>62</v>
+      </c>
+      <c r="M36">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="15">
+        <f>B36*0.82</f>
+        <v>16.172583842404851</v>
+      </c>
+      <c r="F37" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37">
+        <v>0.99</v>
+      </c>
+      <c r="I37" t="s">
+        <v>58</v>
+      </c>
+      <c r="J37">
+        <v>0.98</v>
+      </c>
+      <c r="L37" t="s">
+        <v>63</v>
+      </c>
+      <c r="M37">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="15">
+        <v>0.95</v>
+      </c>
+      <c r="F38" t="s">
+        <v>48</v>
+      </c>
+      <c r="G38">
+        <v>0.99</v>
+      </c>
+      <c r="L38" t="s">
+        <v>64</v>
+      </c>
+      <c r="M38">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="15">
+        <f>B37*B38</f>
+        <v>15.363954650284608</v>
+      </c>
+      <c r="F39" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39">
+        <v>0.96</v>
+      </c>
+      <c r="L39" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="15">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40">
+        <v>0.99</v>
+      </c>
+      <c r="L40" t="s">
+        <v>66</v>
+      </c>
+      <c r="M40">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" s="15">
+        <f>B39*B40</f>
+        <v>15.363954650284608</v>
+      </c>
+      <c r="F41" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41">
+        <v>0.98</v>
+      </c>
+      <c r="L41" t="s">
+        <v>67</v>
+      </c>
+      <c r="M41">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="9">
+        <f>10^(1.325132+0.592471*LOG(B41))</f>
+        <v>106.68432868424418</v>
+      </c>
+      <c r="F42" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42">
+        <v>0.98</v>
+      </c>
+      <c r="L42" t="s">
+        <v>68</v>
+      </c>
+      <c r="M42">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="9">
+        <f>B42/30*22841424.5645393*0.7/10^6</f>
+        <v>56.859181070059186</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="15">
+        <f>G33*J33*M33</f>
+        <v>0.58297945397118356</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" s="15">
+        <f>B39*B46</f>
+        <v>8.9568698928609471</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" s="9">
+        <f>10^(1.325132+0.592471*LOG(B47))</f>
+        <v>77.49201875510424</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="9">
+        <f>B48/30*22841424.5645393*0.7/10^6</f>
+        <v>41.300655684133474</v>
       </c>
     </row>
   </sheetData>
